--- a/data/trans_dic/P44A$sangre-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,12</t>
+          <t>0,0; 34,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,84</t>
+          <t>0,0; 21,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,46; 73,48</t>
+          <t>56,32; 72,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 45,94</t>
+          <t>6,11; 47,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 33,01</t>
+          <t>3,98; 32,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,71; 66,36</t>
+          <t>52,86; 66,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 33,33</t>
+          <t>6,3; 34,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 20,74</t>
+          <t>2,93; 20,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,97; 67,55</t>
+          <t>56,99; 67,83</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 30,91</t>
+          <t>3,52; 31,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 30,24</t>
+          <t>6,91; 30,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,11; 96,78</t>
+          <t>65,04; 96,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,19</t>
+          <t>0,0; 13,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,76</t>
+          <t>0,0; 19,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,16; 76,54</t>
+          <t>65,16; 76,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 14,58</t>
+          <t>1,61; 13,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 20,27</t>
+          <t>5,13; 19,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67,57; 95,46</t>
+          <t>67,15; 94,7</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 29,57</t>
+          <t>3,6; 28,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 23,56</t>
+          <t>2,8; 25,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,17; 69,79</t>
+          <t>52,0; 69,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 28,5</t>
+          <t>3,62; 29,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,39</t>
+          <t>0,0; 27,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,44; 83,52</t>
+          <t>69,15; 84,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 22,2</t>
+          <t>5,74; 26,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 18,46</t>
+          <t>2,15; 17,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,97; 73,59</t>
+          <t>61,72; 73,48</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,88; 43,19</t>
+          <t>14,79; 45,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 23,03</t>
+          <t>4,4; 22,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,87; 70,45</t>
+          <t>59,18; 71,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,54</t>
+          <t>0,0; 28,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 22,77</t>
+          <t>2,63; 22,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,05; 78,61</t>
+          <t>68,43; 78,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 30,51</t>
+          <t>10,09; 29,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 17,63</t>
+          <t>5,24; 18,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,72; 73,63</t>
+          <t>65,45; 73,26</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 28,27</t>
+          <t>11,18; 27,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 16,74</t>
+          <t>6,56; 16,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,62; 89,68</t>
+          <t>63,29; 90,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 15,61</t>
+          <t>3,86; 15,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,01</t>
+          <t>3,62; 13,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,69; 73,86</t>
+          <t>67,7; 73,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 19,08</t>
+          <t>9,16; 18,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 13,74</t>
+          <t>6,41; 13,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,75; 85,69</t>
+          <t>67,02; 86,69</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6403</t>
+          <t>0; 5248</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 8599</t>
+          <t>0; 6669</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51878; 67526</t>
+          <t>51753; 66957</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>935; 6982</t>
+          <t>928; 7168</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1003; 8439</t>
+          <t>1018; 8272</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51395; 64697</t>
+          <t>51534; 64418</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1110; 10132</t>
+          <t>1916; 10387</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1268; 11709</t>
+          <t>1656; 11708</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>107894; 127943</t>
+          <t>107939; 128460</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>890; 8153</t>
+          <t>930; 8192</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2002; 11946</t>
+          <t>2730; 11858</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>248100; 374530</t>
+          <t>251674; 375139</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5162</t>
+          <t>0; 4947</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6319</t>
+          <t>0; 6700</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82878; 97353</t>
+          <t>82874; 97268</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1021; 9146</t>
+          <t>1009; 8723</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3930; 14835</t>
+          <t>3752; 14392</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>347421; 490802</t>
+          <t>345243; 486901</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>996; 7792</t>
+          <t>948; 7533</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>849; 7253</t>
+          <t>862; 7735</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56705; 74434</t>
+          <t>55456; 74504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>970; 7531</t>
+          <t>958; 7835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5562</t>
+          <t>0; 5628</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50210; 60389</t>
+          <t>49997; 60808</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2137; 11715</t>
+          <t>3031; 13969</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1064; 9431</t>
+          <t>1098; 9170</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>110898; 131698</t>
+          <t>110452; 131492</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5751; 17893</t>
+          <t>6128; 18673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2431; 13473</t>
+          <t>2575; 13155</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>112568; 134699</t>
+          <t>113156; 135936</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 7397</t>
+          <t>0; 8367</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>955; 8330</t>
+          <t>961; 8094</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>123260; 142381</t>
+          <t>123944; 141895</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7235; 21477</t>
+          <t>7104; 20600</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4922; 16767</t>
+          <t>4985; 17343</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>244706; 274153</t>
+          <t>243682; 272746</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12122; 30912</t>
+          <t>12226; 29752</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10801; 26726</t>
+          <t>10482; 26977</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>494134; 696550</t>
+          <t>491588; 699871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4504; 16699</t>
+          <t>4125; 16680</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4410; 16270</t>
+          <t>4200; 15993</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>323638; 353144</t>
+          <t>323663; 351987</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19953; 41268</t>
+          <t>19817; 40649</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17810; 37903</t>
+          <t>17675; 38486</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837575; 1075311</t>
+          <t>840970; 1087759</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$sangre-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,53</t>
+          <t>0,0; 40,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,59</t>
+          <t>0,0; 27,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,32; 72,87</t>
+          <t>53,79; 71,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 47,16</t>
+          <t>6,11; 46,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 32,36</t>
+          <t>3,95; 34,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,86; 66,07</t>
+          <t>52,55; 66,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 34,17</t>
+          <t>6,4; 33,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 20,74</t>
+          <t>2,84; 20,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,99; 67,83</t>
+          <t>56,02; 66,65</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>68,07%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 31,06</t>
+          <t>3,44; 29,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 30,02</t>
+          <t>6,06; 27,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,04; 96,94</t>
+          <t>58,49; 72,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,6</t>
+          <t>0,0; 13,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,89</t>
+          <t>0,0; 18,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,16; 76,48</t>
+          <t>64,77; 76,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 13,9</t>
+          <t>1,64; 15,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 19,67</t>
+          <t>5,26; 20,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67,15; 94,7</t>
+          <t>62,88; 72,02</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>66,17%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 28,58</t>
+          <t>3,56; 29,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 25,12</t>
+          <t>2,81; 25,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,0; 69,86</t>
+          <t>50,32; 67,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 29,65</t>
+          <t>3,64; 29,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,72</t>
+          <t>0,0; 27,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,15; 84,1</t>
+          <t>68,28; 82,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 26,47</t>
+          <t>5,59; 24,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 17,95</t>
+          <t>2,14; 19,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,72; 73,48</t>
+          <t>59,99; 72,05</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,79; 45,07</t>
+          <t>15,07; 44,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 22,49</t>
+          <t>4,55; 23,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,18; 71,1</t>
+          <t>59,92; 71,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,89</t>
+          <t>0,0; 22,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 22,12</t>
+          <t>0,0; 20,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,43; 78,34</t>
+          <t>68,4; 78,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 29,26</t>
+          <t>10,09; 31,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 18,24</t>
+          <t>5,06; 18,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,45; 73,26</t>
+          <t>66,28; 73,63</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,18; 27,2</t>
+          <t>11,44; 28,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 16,89</t>
+          <t>6,16; 16,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,29; 90,1</t>
+          <t>60,42; 68,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 15,6</t>
+          <t>4,09; 15,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 13,77</t>
+          <t>3,84; 15,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,7; 73,62</t>
+          <t>67,39; 73,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 18,79</t>
+          <t>9,05; 19,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,41; 13,95</t>
+          <t>6,64; 14,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67,02; 86,69</t>
+          <t>64,9; 69,48</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59575</t>
+          <t>64191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58263</t>
+          <t>63489</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>117838</t>
+          <t>127681</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5248</t>
+          <t>0; 6122</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6669</t>
+          <t>0; 8360</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51753; 66957</t>
+          <t>54235; 71913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>928; 7168</t>
+          <t>928; 7142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1018; 8272</t>
+          <t>1009; 8701</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51534; 64418</t>
+          <t>55648; 69901</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1916; 10387</t>
+          <t>1945; 10155</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1656; 11708</t>
+          <t>1601; 11604</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>107939; 128460</t>
+          <t>115814; 137787</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>339415</t>
+          <t>100933</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>99409</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>429923</t>
+          <t>200342</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>930; 8192</t>
+          <t>909; 7703</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2730; 11858</t>
+          <t>2395; 10886</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>251674; 375139</t>
+          <t>90050; 111582</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4947</t>
+          <t>0; 4978</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6700</t>
+          <t>0; 6369</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82874; 97268</t>
+          <t>90893; 106883</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1009; 8723</t>
+          <t>1027; 9561</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3752; 14392</t>
+          <t>3847; 14908</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>345243; 486901</t>
+          <t>185053; 211961</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>70019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55952</t>
+          <t>64405</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>121269</t>
+          <t>134424</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>948; 7533</t>
+          <t>938; 7849</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>862; 7735</t>
+          <t>866; 7956</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55456; 74504</t>
+          <t>59414; 79426</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>958; 7835</t>
+          <t>961; 7686</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5628</t>
+          <t>0; 5615</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49997; 60808</t>
+          <t>58094; 70071</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3031; 13969</t>
+          <t>2950; 13180</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1098; 9170</t>
+          <t>1094; 9888</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>110452; 131492</t>
+          <t>121880; 146368</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124738</t>
+          <t>131099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>133284</t>
+          <t>145600</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>258021</t>
+          <t>276698</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6128; 18673</t>
+          <t>6242; 18470</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2575; 13155</t>
+          <t>2660; 13788</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>113156; 135936</t>
+          <t>118646; 141981</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 8367</t>
+          <t>0; 6558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>961; 8094</t>
+          <t>0; 7584</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>123944; 141895</t>
+          <t>134725; 154571</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7104; 20600</t>
+          <t>7102; 22374</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4985; 17343</t>
+          <t>4813; 17751</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>243682; 272746</t>
+          <t>261772; 290827</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>589045</t>
+          <t>366242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>338007</t>
+          <t>372902</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>927052</t>
+          <t>739144</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12226; 29752</t>
+          <t>12508; 30662</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10482; 26977</t>
+          <t>9844; 25970</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>491588; 699871</t>
+          <t>344945; 388744</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4125; 16680</t>
+          <t>4369; 16111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4200; 15993</t>
+          <t>4458; 17587</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>323663; 351987</t>
+          <t>356019; 388187</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19817; 40649</t>
+          <t>19570; 42080</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17675; 38486</t>
+          <t>18302; 38607</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840970; 1087759</t>
+          <t>713361; 763640</t>
         </is>
       </c>
     </row>
